--- a/data/2026/cjsl/fall/soccer-fun-for-kids-brooklyn-patriots-2014-2015-blue.xlsx
+++ b/data/2026/cjsl/fall/soccer-fun-for-kids-brooklyn-patriots-2014-2015-blue.xlsx
@@ -78,7 +78,7 @@
     <col min="6" max="6" bestFit="1" customWidth="1" width="41.800000000000004"/>
     <col min="7" max="7" bestFit="1" customWidth="1" width="47.300000000000004"/>
     <col min="8" max="8" bestFit="1" customWidth="1" width="20.900000000000002"/>
-    <col min="9" max="9" bestFit="1" customWidth="1" width="11.0"/>
+    <col min="9" max="9" bestFit="1" customWidth="1" width="12.100000000000001"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -175,21 +175,21 @@
     </row>
     <row r="3">
       <c r="A3" s="0" t="n">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B3" s="0" t="inlineStr">
         <is>
-          <t>Sunday, September 27, 2026</t>
+          <t>Saturday, October  3, 2026</t>
         </is>
       </c>
       <c r="C3" s="0" t="inlineStr">
         <is>
-          <t>12:15 EDT</t>
+          <t>14:45 EDT</t>
         </is>
       </c>
       <c r="D3" s="0" t="inlineStr">
         <is>
-          <t>Soccer Fun for Kids / Brooklyn Patriots 2014-2015 Blue</t>
+          <t>Veras Soccer Academy V.S.A Prospects (2014-2015) cjsl</t>
         </is>
       </c>
       <c r="E3" s="0" t="inlineStr">
@@ -199,12 +199,12 @@
       </c>
       <c r="F3" s="0" t="inlineStr">
         <is>
-          <t>ARB SC 1415</t>
+          <t>Soccer Fun for Kids / Brooklyn Patriots 2014-2015 Blue</t>
         </is>
       </c>
       <c r="G3" s="0" t="inlineStr">
         <is>
-          <t>Prospect Park, Parade Grounds Field 7A - Parade Grounds Field 7A</t>
+          <t>St. Michaels Playground - St. Michaels Playground</t>
         </is>
       </c>
       <c r="H3" s="0" t="inlineStr">
@@ -214,68 +214,72 @@
       </c>
       <c r="I3" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Scheduled</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="n">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="B4" s="0" t="inlineStr">
         <is>
-          <t>Saturday, October  3, 2026</t>
+          <t>Sunday, October 25, 2026</t>
         </is>
       </c>
       <c r="C4" s="0" t="inlineStr">
         <is>
+          <t>12:15 EDT</t>
+        </is>
+      </c>
+      <c r="D4" s="0" t="inlineStr">
+        <is>
+          <t>Soccer Fun for Kids / Brooklyn Patriots 2014-2015 Blue</t>
+        </is>
+      </c>
+      <c r="E4" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F4" s="0" t="inlineStr">
+        <is>
+          <t>Long Island City Soccer Club 2014/2015</t>
+        </is>
+      </c>
+      <c r="G4" s="0" t="inlineStr">
+        <is>
+          <t>Prospect Park, Parade Grounds Field 7A - Parade Grounds Field 7A</t>
+        </is>
+      </c>
+      <c r="H4" s="0" t="inlineStr">
+        <is>
+          <t>U12 (9v9) - Super D1</t>
+        </is>
+      </c>
+      <c r="I4" s="0" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="D4" s="0" t="inlineStr">
-        <is>
-          <t>Veras Soccer Academy V.S.A Prospects (2014-2015) cjsl</t>
-        </is>
-      </c>
-      <c r="E4" s="0" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F4" s="0" t="inlineStr">
-        <is>
-          <t>Soccer Fun for Kids / Brooklyn Patriots 2014-2015 Blue</t>
-        </is>
-      </c>
-      <c r="G4" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H4" s="0" t="inlineStr">
-        <is>
-          <t>U12 (9v9) - Super D1</t>
-        </is>
-      </c>
-      <c r="I4" s="0"/>
     </row>
     <row r="5">
       <c r="A5" s="0" t="n">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B5" s="0" t="inlineStr">
         <is>
-          <t>Sunday, October 25, 2026</t>
+          <t>Saturday, October 31, 2026</t>
         </is>
       </c>
       <c r="C5" s="0" t="inlineStr">
         <is>
-          <t>12:15 EDT</t>
+          <t>08:30 EDT</t>
         </is>
       </c>
       <c r="D5" s="0" t="inlineStr">
         <is>
-          <t>Soccer Fun for Kids / Brooklyn Patriots 2014-2015 Blue</t>
+          <t>ARB SC 1415</t>
         </is>
       </c>
       <c r="E5" s="0" t="inlineStr">
@@ -285,12 +289,12 @@
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
-          <t>Long Island City Soccer Club 2014/2015</t>
+          <t>Soccer Fun for Kids / Brooklyn Patriots 2014-2015 Blue</t>
         </is>
       </c>
       <c r="G5" s="0" t="inlineStr">
         <is>
-          <t>Prospect Park, Parade Grounds Field 7A - Parade Grounds Field 7A</t>
+          <t>Frank Principe Park  - Full Field</t>
         </is>
       </c>
       <c r="H5" s="0" t="inlineStr">
@@ -306,21 +310,21 @@
     </row>
     <row r="6">
       <c r="A6" s="0" t="n">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="B6" s="0" t="inlineStr">
         <is>
-          <t>Saturday, October 31, 2026</t>
+          <t>Sunday, November  8, 2026</t>
         </is>
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
-          <t>08:30 EDT</t>
+          <t>13:30 EST</t>
         </is>
       </c>
       <c r="D6" s="0" t="inlineStr">
         <is>
-          <t>ARB SC 1415</t>
+          <t>Soccer Fun for Kids / Brooklyn Patriots 2014-2015 Blue</t>
         </is>
       </c>
       <c r="E6" s="0" t="inlineStr">
@@ -330,12 +334,12 @@
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
-          <t>Soccer Fun for Kids / Brooklyn Patriots 2014-2015 Blue</t>
+          <t>Veras Soccer Academy V.S.A Prospects (2014-2015) cjsl</t>
         </is>
       </c>
       <c r="G6" s="0" t="inlineStr">
         <is>
-          <t>Frank Principe Park  - Full Field</t>
+          <t>Prospect Park, Parade Grounds Field 7A - Parade Grounds Field 7A</t>
         </is>
       </c>
       <c r="H6" s="0" t="inlineStr">
@@ -351,11 +355,11 @@
     </row>
     <row r="7">
       <c r="A7" s="0" t="n">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="B7" s="0" t="inlineStr">
         <is>
-          <t>Sunday, November  8, 2026</t>
+          <t>Sunday, November 15, 2026</t>
         </is>
       </c>
       <c r="C7" s="0" t="inlineStr">
@@ -375,7 +379,7 @@
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
-          <t>Veras Soccer Academy V.S.A Prospects (2014-2015) cjsl</t>
+          <t>ARB SC 1415</t>
         </is>
       </c>
       <c r="G7" s="0" t="inlineStr">
@@ -390,7 +394,7 @@
       </c>
       <c r="I7" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Rescheduled</t>
         </is>
       </c>
     </row>

--- a/data/2026/cjsl/fall/soccer-fun-for-kids-brooklyn-patriots-2014-2015-blue.xlsx
+++ b/data/2026/cjsl/fall/soccer-fun-for-kids-brooklyn-patriots-2014-2015-blue.xlsx
@@ -194,7 +194,7 @@
       </c>
       <c r="E3" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2 - 1</t>
         </is>
       </c>
       <c r="F3" s="0" t="inlineStr">

--- a/data/2026/cjsl/fall/soccer-fun-for-kids-brooklyn-patriots-2014-2015-blue.xlsx
+++ b/data/2026/cjsl/fall/soccer-fun-for-kids-brooklyn-patriots-2014-2015-blue.xlsx
@@ -239,7 +239,7 @@
       </c>
       <c r="E4" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2 - 2</t>
         </is>
       </c>
       <c r="F4" s="0" t="inlineStr">
